--- a/Evaluación de métricas.xlsx
+++ b/Evaluación de métricas.xlsx
@@ -1,31 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Claudia\OneDrive\Documentos\FCFM\TesinaMCD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8cd99136cfcc98d8/Documentos/FCFM/TesinaMCD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4D00DD-8E8B-4DA4-8141-A139AE06F642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="13_ncr:1_{FA4D00DD-8E8B-4DA4-8141-A139AE06F642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{157C48A6-D3AE-4E37-BC67-2EE22FB50008}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{D195F59A-6A96-4642-803F-E5122D0BFA4A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{D195F59A-6A96-4642-803F-E5122D0BFA4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId6"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId9"/>
+    <sheet name="Sheet10" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId7"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId9"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId10"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId10"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -47,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="58">
   <si>
     <t>Light GBM</t>
   </si>
@@ -74,12 +72,6 @@
   </si>
   <si>
     <t>Completo 0.35</t>
-  </si>
-  <si>
-    <t>Kmeans 0.10</t>
-  </si>
-  <si>
-    <t>Kmeans 0.35</t>
   </si>
   <si>
     <t>GMM 0.10</t>
@@ -173,9 +165,6 @@
     <t>Prom</t>
   </si>
   <si>
-    <t>KMeans 0.35</t>
-  </si>
-  <si>
     <t>Naive</t>
   </si>
   <si>
@@ -225,9 +214,6 @@
     <t>Forecasting a Short-Term Photovoltaic Power Model Based on Improved Snake Optimization, Convolutional Neural Network, and Bidirectional Long Short-Term Memory Network</t>
   </si>
   <si>
-    <t>KMeans 0.10</t>
-  </si>
-  <si>
     <t>CT-NET</t>
   </si>
   <si>
@@ -239,12 +225,21 @@
   <si>
     <t>CNN-BiLSTM Nublado</t>
   </si>
+  <si>
+    <t>R²</t>
+  </si>
+  <si>
+    <t>K-Medias 0.35</t>
+  </si>
+  <si>
+    <t>K-Medias 0.10</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,13 +268,49 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF5050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -295,17 +326,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -317,7 +342,42 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -325,6 +385,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF5050"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -366,15 +431,298 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Light GBM</c:v>
+                  <c:v>LightGBM</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:shade val="56000"/>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Completo 0.10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Completo 0.35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>K-Medias 0.10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>K-Medias 0.35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GMM 0.10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GMM 0.35</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7.0122516411383229E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.32670737058406263</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31805234078900702</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5734621376007052E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.7766161599484427E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.11231620155894273</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-58CD-4AB1-8FA2-E3859020CCD0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Random Forest</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Completo 0.10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Completo 0.35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>K-Medias 0.10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>K-Medias 0.35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>GMM 0.10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>GMM 0.35</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$3:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.38457372015273483</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.31601955663342807</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.18934686381159205</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.47543382139820989</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.5754354891843354E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.42015084914615164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-58CD-4AB1-8FA2-E3859020CCD0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CT-NET</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -453,10 +801,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -469,55 +817,56 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$8</c:f>
+              <c:f>Sheet1!$J$3:$J$8</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.0122516411383229E-2</c:v>
+                  <c:v>0.15838266323240724</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.32670737058406263</c:v>
+                  <c:v>0.13992449201269586</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.31805234078900702</c:v>
+                  <c:v>0.12550060050430889</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.5734621376007052E-2</c:v>
+                  <c:v>0.11179371608441602</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.7766161599484427E-2</c:v>
+                  <c:v>6.0874381780259501E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.11231620155894273</c:v>
+                  <c:v>0.27556106273640579</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-58CD-4AB1-8FA2-E3859020CCD0}"/>
+              <c16:uniqueId val="{00000008-58CD-4AB1-8FA2-E3859020CCD0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="11"/>
+          <c:order val="11"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$1</c:f>
+              <c:f>Sheet1!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Random Forest</c:v>
+                  <c:v>CNN-BiLSTM</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:shade val="82000"/>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -596,10 +945,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -612,56 +961,54 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$3:$G$8</c:f>
+              <c:f>Sheet1!$M$3:$M$8</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.38457372015273483</c:v>
+                  <c:v>9.9326929358187099E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.31601955663342807</c:v>
+                  <c:v>2.3715018712115121E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.18934686381159205</c:v>
+                  <c:v>0.25910817447325241</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.47543382139820989</c:v>
+                  <c:v>0.21071109230448681</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.5754354891843354E-2</c:v>
+                  <c:v>0.16515959338117869</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.42015084914615164</c:v>
+                  <c:v>0.26712919781683375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-58CD-4AB1-8FA2-E3859020CCD0}"/>
+              <c16:uniqueId val="{0000000B-58CD-4AB1-8FA2-E3859020CCD0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="8"/>
-          <c:order val="8"/>
+          <c:idx val="14"/>
+          <c:order val="14"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$1</c:f>
+              <c:f>Sheet1!$N$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>CT-NET</c:v>
+                  <c:v>QR-CNN-BiGRU-Attention</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:tint val="92000"/>
-              </a:schemeClr>
+              <a:srgbClr val="FFC000"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -670,6 +1017,28 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="9.7550143706654158E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-BE09-4024-B2C0-E01A50316905}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -739,296 +1108,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>GMM 0.10</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>GMM 0.35</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$J$3:$J$8</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>0.15838266323240724</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13992449201269586</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.12550060050430889</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.11179371608441602</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.0874381780259501E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.27556106273640579</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-58CD-4AB1-8FA2-E3859020CCD0}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="11"/>
-          <c:order val="11"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>CNN-BiLSTM</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:tint val="65000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$3:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>Completo 0.10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Completo 0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>GMM 0.10</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>GMM 0.35</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$M$3:$M$8</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>9.9326929358187099E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.3715018712115121E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.25910817447325241</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.21071109230448681</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.16515959338117869</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.26712919781683375</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-58CD-4AB1-8FA2-E3859020CCD0}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="14"/>
-          <c:order val="14"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$N$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>QR-CNN-BiGRU-Attention</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:tint val="39000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$3:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>Completo 0.10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Completo 0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -1103,7 +1186,7 @@
                     <c:strCache>
                       <c:ptCount val="2"/>
                       <c:pt idx="0">
-                        <c:v>Light GBM</c:v>
+                        <c:v>LightGBM</c:v>
                       </c:pt>
                       <c:pt idx="1">
                         <c:v>Entrenamiento</c:v>
@@ -1199,10 +1282,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -1259,7 +1342,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$C$1:$C$2</c15:sqref>
@@ -1269,7 +1352,7 @@
                     <c:strCache>
                       <c:ptCount val="2"/>
                       <c:pt idx="0">
-                        <c:v>Light GBM</c:v>
+                        <c:v>LightGBM</c:v>
                       </c:pt>
                       <c:pt idx="1">
                         <c:v>Prueba</c:v>
@@ -1327,7 +1410,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -1349,7 +1432,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -1365,10 +1448,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -1381,7 +1464,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$C$3:$C$8</c15:sqref>
@@ -1412,7 +1495,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -1425,7 +1508,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$E$1:$E$2</c15:sqref>
@@ -1493,7 +1576,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -1515,7 +1598,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -1531,10 +1614,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -1547,7 +1630,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$E$3:$E$8</c15:sqref>
@@ -1578,7 +1661,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -1591,7 +1674,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$F$1:$F$2</c15:sqref>
@@ -1659,7 +1742,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -1681,7 +1764,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -1697,10 +1780,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -1713,7 +1796,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$F$3:$F$8</c15:sqref>
@@ -1744,7 +1827,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -1757,7 +1840,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$H$1:$H$2</c15:sqref>
@@ -1825,7 +1908,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -1847,7 +1930,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -1863,10 +1946,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -1879,7 +1962,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$H$3:$H$8</c15:sqref>
@@ -1910,7 +1993,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000006-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -1923,7 +2006,7 @@
                 <c:order val="7"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$1:$I$2</c15:sqref>
@@ -1989,7 +2072,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2011,7 +2094,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -2027,10 +2110,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -2043,7 +2126,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$3:$I$8</c15:sqref>
@@ -2074,7 +2157,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000007-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -2087,7 +2170,7 @@
                 <c:order val="9"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$K$1:$K$2</c15:sqref>
@@ -2155,7 +2238,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2177,7 +2260,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -2193,10 +2276,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -2209,7 +2292,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$K$3:$K$8</c15:sqref>
@@ -2240,7 +2323,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000009-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -2253,7 +2336,7 @@
                 <c:order val="10"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$L$1:$L$2</c15:sqref>
@@ -2321,7 +2404,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2343,7 +2426,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -2359,10 +2442,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -2375,7 +2458,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$L$3:$L$8</c15:sqref>
@@ -2406,7 +2489,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000A-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -2419,7 +2502,7 @@
                 <c:order val="12"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$1:$N$2</c15:sqref>
@@ -2487,7 +2570,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2509,7 +2592,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -2525,10 +2608,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -2541,7 +2624,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$3:$N$8</c15:sqref>
@@ -2572,7 +2655,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000C-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -2585,7 +2668,7 @@
                 <c:order val="13"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$O$2</c15:sqref>
@@ -2653,7 +2736,7 @@
                   <c:showPercent val="0"/>
                   <c:showBubbleSize val="0"/>
                   <c:showLeaderLines val="0"/>
-                  <c:extLst>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                     <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
@@ -2675,7 +2758,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$A$3:$A$8</c15:sqref>
@@ -2691,10 +2774,10 @@
                         <c:v>Completo 0.35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>KMeans 0.10</c:v>
+                        <c:v>K-Medias 0.10</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>KMeans 0.35</c:v>
+                        <c:v>K-Medias 0.35</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>GMM 0.10</c:v>
@@ -2707,7 +2790,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$3:$O$8</c15:sqref>
@@ -2738,7 +2821,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000D-58CD-4AB1-8FA2-E3859020CCD0}"/>
                   </c:ext>
@@ -4012,15 +4095,320 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Light GBM</c:v>
+                  <c:v>LightGBM</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:shade val="53000"/>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$B$28:$G$29</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="6"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Comp. 0.10</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Comp. 0.35</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Comp. 0.10</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Comp. 0.35</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Comp. 0.10</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Comp. 0.35</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>RMSE</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>MAE</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>R²</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$30:$G$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.128178046673578</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.105562013930288</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0494413632082391</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95905123098281442</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96628285341274633</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.96699566624698974</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3B53-4B91-881E-4C8DF51DEF72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Random Forest</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$B$28:$G$29</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="6"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Comp. 0.10</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Comp. 0.35</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Comp. 0.10</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Comp. 0.35</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Comp. 0.10</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Comp. 0.35</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>RMSE</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>MAE</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>R²</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$31:$G$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.207589209059218</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2510727036333349</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.94907410659893265</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.90760134082901345</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.9637196539076307</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.96227632975987243</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3B53-4B91-881E-4C8DF51DEF72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CT-NET</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -4118,7 +4506,7 @@
                     <c:v>MAE</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>R2</c:v>
+                    <c:v>R²</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -4126,55 +4514,56 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$B$30:$G$30</c:f>
+              <c:f>Sheet2!$B$32:$G$32</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.128178046673578</c:v>
+                  <c:v>2.663214627042779</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.105562013930288</c:v>
+                  <c:v>2.769152041163284</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0494413632082391</c:v>
+                  <c:v>1.312878448217691</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.95905123098281442</c:v>
+                  <c:v>1.4387964635510739</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.96628285341274633</c:v>
+                  <c:v>0.9468744235867097</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.96699566624698974</c:v>
+                  <c:v>0.94256390259891798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3B53-4B91-881E-4C8DF51DEF72}"/>
+              <c16:uniqueId val="{00000002-3B53-4B91-881E-4C8DF51DEF72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$A$31</c:f>
+              <c:f>Sheet2!$A$33</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Random Forest</c:v>
+                  <c:v>CNN-BiLSTM</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:shade val="76000"/>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -4272,7 +4661,7 @@
                     <c:v>MAE</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>R2</c:v>
+                    <c:v>R²</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -4280,54 +4669,54 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$B$31:$G$31</c:f>
+              <c:f>Sheet2!$B$33:$G$33</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.207589209059218</c:v>
+                  <c:v>2.837321868384854</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2510727036333349</c:v>
+                  <c:v>2.7449080347887702</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.94907410659893265</c:v>
+                  <c:v>1.461685608320521</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.90760134082901345</c:v>
+                  <c:v>1.399776304499085</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9637196539076307</c:v>
+                  <c:v>0.93970121920264327</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.96227632975987243</c:v>
+                  <c:v>0.94356520948612876</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3B53-4B91-881E-4C8DF51DEF72}"/>
+              <c16:uniqueId val="{00000003-3B53-4B91-881E-4C8DF51DEF72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$A$32</c:f>
+              <c:f>Sheet2!$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>CT-NET</c:v>
+                  <c:v>QR-CNN-BiGRU-Attention</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="FFC000"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4424,315 +4813,7 @@
                     <c:v>MAE</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>R2</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet2!$B$32:$G$32</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>2.663214627042779</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.769152041163284</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.312878448217691</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.4387964635510739</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.9468744235867097</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.94256390259891798</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3B53-4B91-881E-4C8DF51DEF72}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet2!$A$33</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>CNN-BiLSTM</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:tint val="77000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Sheet2!$B$28:$G$29</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="6"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Comp. 0.10</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Comp. 0.35</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Comp. 0.10</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Comp. 0.35</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Comp. 0.10</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Comp. 0.35</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>RMSE</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>MAE</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>R2</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet2!$B$33:$G$33</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>2.837321868384854</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.7449080347887702</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.461685608320521</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.399776304499085</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.93970121920264327</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.94356520948612876</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-3B53-4B91-881E-4C8DF51DEF72}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet2!$A$34</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>QR-CNN-BiGRU-Attention</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:tint val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Sheet2!$B$28:$G$29</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="6"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Comp. 0.10</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Comp. 0.35</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Comp. 0.10</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Comp. 0.35</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Comp. 0.10</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Comp. 0.35</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>RMSE</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>MAE</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>R2</c:v>
+                    <c:v>R²</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -4999,15 +5080,258 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Light GBM</c:v>
+                  <c:v>LightGBM</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:shade val="53000"/>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet7!$B$3:$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>RMSE</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MAE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>R²</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet7!$B$4:$D$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2.128178046673578</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0494413632082391</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.96628285341274633</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4C30-467D-8338-A2905408454B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet7!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Random Forest</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet7!$B$3:$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>RMSE</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>MAE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>R²</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet7!$B$5:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2.207589209059218</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94907410659893265</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9637196539076307</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4C30-467D-8338-A2905408454B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet7!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CT-NET</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -5084,53 +5408,54 @@
                   <c:v>MAE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>R2</c:v>
+                  <c:v>R²</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet7!$B$4:$D$4</c:f>
+              <c:f>Sheet7!$B$6:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>2.128178046673578</c:v>
+                  <c:v>2.663214627042779</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0494413632082391</c:v>
+                  <c:v>1.312878448217691</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.96628285341274633</c:v>
+                  <c:v>0.9468744235867097</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4C30-467D-8338-A2905408454B}"/>
+              <c16:uniqueId val="{00000002-4C30-467D-8338-A2905408454B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet7!$A$5</c:f>
+              <c:f>Sheet7!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Random Forest</c:v>
+                  <c:v>CNN-BiLSTM</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:shade val="76000"/>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -5207,52 +5532,52 @@
                   <c:v>MAE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>R2</c:v>
+                  <c:v>R²</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet7!$B$5:$D$5</c:f>
+              <c:f>Sheet7!$B$7:$D$7</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>2.207589209059218</c:v>
+                  <c:v>2.837321868384854</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.94907410659893265</c:v>
+                  <c:v>1.461685608320521</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9637196539076307</c:v>
+                  <c:v>0.93970121920264327</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4C30-467D-8338-A2905408454B}"/>
+              <c16:uniqueId val="{00000003-4C30-467D-8338-A2905408454B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet7!$A$6</c:f>
+              <c:f>Sheet7!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>CT-NET</c:v>
+                  <c:v>QR-CNN-BiGRU-Attention</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="FFC000"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5328,253 +5653,7 @@
                   <c:v>MAE</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>R2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet7!$B$6:$D$6</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>2.663214627042779</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.312878448217691</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.9468744235867097</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4C30-467D-8338-A2905408454B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet7!$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>CNN-BiLSTM</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:tint val="77000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet7!$B$3:$D$3</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>RMSE</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>MAE</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>R2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet7!$B$7:$D$7</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>2.837321868384854</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.461685608320521</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.93970121920264327</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4C30-467D-8338-A2905408454B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet7!$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>QR-CNN-BiGRU-Attention</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:tint val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet7!$B$3:$D$3</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>RMSE</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>MAE</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>R2</c:v>
+                  <c:v>R²</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5790,8 +5869,9 @@
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -5808,29 +5888,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="34925" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="34925">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet6!$C$2:$C$7</c:f>
@@ -5843,10 +5911,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -5884,7 +5952,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-ECEF-47C6-9695-2FAFCA4DE01B}"/>
@@ -5900,35 +5967,21 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Light GBM</c:v>
+                  <c:v>LightGBM</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet6!$C$2:$C$7</c:f>
@@ -5941,10 +5994,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -5962,7 +6015,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.128178046673578</c:v>
+                  <c:v>2.1281780466735798</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2.105562013930288</c:v>
@@ -5982,7 +6035,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-ECEF-47C6-9695-2FAFCA4DE01B}"/>
@@ -6004,29 +6056,15 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:srgbClr val="FF5050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet6!$C$2:$C$7</c:f>
@@ -6039,10 +6077,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -6080,7 +6118,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-ECEF-47C6-9695-2FAFCA4DE01B}"/>
@@ -6102,29 +6139,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet6!$C$2:$C$7</c:f>
@@ -6137,10 +6163,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -6178,7 +6204,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-ECEF-47C6-9695-2FAFCA4DE01B}"/>
@@ -6200,29 +6225,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet6!$C$2:$C$7</c:f>
@@ -6235,10 +6249,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -6276,7 +6290,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-ECEF-47C6-9695-2FAFCA4DE01B}"/>
@@ -6298,29 +6311,15 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet6!$C$2:$C$7</c:f>
@@ -6333,10 +6332,10 @@
                   <c:v>Completo 0.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>KMeans 0.10</c:v>
+                  <c:v>K-Medias 0.10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>KMeans 0.35</c:v>
+                  <c:v>K-Medias 0.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>GMM 0.10</c:v>
@@ -6374,7 +6373,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-ECEF-47C6-9695-2FAFCA4DE01B}"/>
@@ -6389,11 +6387,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
+        <c:gapWidth val="150"/>
         <c:axId val="1500067376"/>
         <c:axId val="1500063536"/>
-      </c:lineChart>
+      </c:barChart>
       <c:catAx>
         <c:axId val="1500067376"/>
         <c:scaling>
@@ -6669,8 +6666,8 @@
           <c:yMode val="edge"/>
           <c:x val="8.5052206698814997E-2"/>
           <c:y val="3.7322035145376291E-2"/>
-          <c:w val="0.24334307312741912"/>
-          <c:h val="0.38325555702957698"/>
+          <c:w val="0.16969114553604719"/>
+          <c:h val="0.36202983608929712"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -9331,7 +9328,7 @@
       <xdr:col>17</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>21907</xdr:rowOff>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9482,15 +9479,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>504826</xdr:colOff>
+      <xdr:colOff>506731</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>54292</xdr:rowOff>
+      <xdr:rowOff>58102</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>480060</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9518,22 +9515,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9860,31 +9841,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
@@ -9894,7 +9875,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -9903,7 +9884,7 @@
         <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
@@ -9912,7 +9893,7 @@
         <v>6</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
         <v>5</v>
@@ -9921,7 +9902,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N2" t="s">
         <v>5</v>
@@ -9930,7 +9911,7 @@
         <v>6</v>
       </c>
       <c r="P2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -9943,7 +9924,7 @@
       <c r="C3">
         <v>2.128178046673578</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <f>C3/B3-1</f>
         <v>7.0122516411383229E-2</v>
       </c>
@@ -9953,7 +9934,7 @@
       <c r="F3">
         <v>2.207589209059218</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <f>F3/E3-1</f>
         <v>0.38457372015273483</v>
       </c>
@@ -9963,7 +9944,7 @@
       <c r="I3">
         <v>2.663214627042779</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <f>I3/H3-1</f>
         <v>0.15838266323240724</v>
       </c>
@@ -9973,7 +9954,7 @@
       <c r="L3">
         <v>2.837321868384854</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <f>L3/K3-1</f>
         <v>9.9326929358187099E-2</v>
       </c>
@@ -9983,7 +9964,7 @@
       <c r="O3">
         <v>2.568287972462524</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <f>O3/N3-1</f>
         <v>0.10147359302467218</v>
       </c>
@@ -9998,7 +9979,7 @@
       <c r="C4">
         <v>2.105562013930288</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <f t="shared" ref="D4:D8" si="0">C4/B4-1</f>
         <v>0.32670737058406263</v>
       </c>
@@ -10008,7 +9989,7 @@
       <c r="F4">
         <v>2.2510727036333349</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G8" si="1">F4/E4-1</f>
         <v>0.31601955663342807</v>
       </c>
@@ -10018,7 +9999,7 @@
       <c r="I4">
         <v>2.769152041163284</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <f t="shared" ref="J4:J8" si="2">I4/H4-1</f>
         <v>0.13992449201269586</v>
       </c>
@@ -10028,7 +10009,7 @@
       <c r="L4">
         <v>2.7449080347887702</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="1">
         <f t="shared" ref="M4:M8" si="3">L4/K4-1</f>
         <v>2.3715018712115121E-2</v>
       </c>
@@ -10038,14 +10019,14 @@
       <c r="O4">
         <v>2.5303852308873829</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <f t="shared" ref="P4:P8" si="4">O4/N4-1</f>
         <v>-1.0827096281033732E-2</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>1.7436159480948865</v>
@@ -10053,7 +10034,7 @@
       <c r="C5">
         <v>2.2981770818235088</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <f t="shared" si="0"/>
         <v>0.31805234078900702</v>
       </c>
@@ -10063,7 +10044,7 @@
       <c r="F5">
         <v>2.3352707322188273</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <f t="shared" si="1"/>
         <v>0.18934686381159205</v>
       </c>
@@ -10073,7 +10054,7 @@
       <c r="I5">
         <v>6.0375504554926405</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <f t="shared" si="2"/>
         <v>0.12550060050430889</v>
       </c>
@@ -10083,7 +10064,7 @@
       <c r="L5">
         <v>11.361428245732366</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <f t="shared" si="3"/>
         <v>0.25910817447325241</v>
       </c>
@@ -10093,14 +10074,14 @@
       <c r="O5">
         <v>5.9549307792865864</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <f t="shared" si="4"/>
         <v>0.21961199193073333</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <v>2.1244172771434888</v>
@@ -10108,7 +10089,7 @@
       <c r="C6">
         <v>2.2640650425011639</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <f t="shared" si="0"/>
         <v>6.5734621376007052E-2</v>
       </c>
@@ -10118,7 +10099,7 @@
       <c r="F6">
         <v>2.5181998556131502</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <f t="shared" si="1"/>
         <v>0.47543382139820989</v>
       </c>
@@ -10128,7 +10109,7 @@
       <c r="I6">
         <v>5.0437205099435367</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <f t="shared" si="2"/>
         <v>0.11179371608441602</v>
       </c>
@@ -10138,7 +10119,7 @@
       <c r="L6">
         <v>5.4623510188892332</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <f t="shared" si="3"/>
         <v>0.21071109230448681</v>
       </c>
@@ -10148,14 +10129,14 @@
       <c r="O6">
         <v>4.7578090316455341</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <f t="shared" si="4"/>
         <v>0.18841977421555933</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1.9757191393323466</v>
@@ -10163,7 +10144,7 @@
       <c r="C7">
         <v>2.0503344676235664</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <f t="shared" si="0"/>
         <v>3.7766161599484427E-2</v>
       </c>
@@ -10173,7 +10154,7 @@
       <c r="F7">
         <v>2.1745480191730437</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <f t="shared" si="1"/>
         <v>8.5754354891843354E-2</v>
       </c>
@@ -10183,7 +10164,7 @@
       <c r="I7">
         <v>9.5311051900475423</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <f t="shared" si="2"/>
         <v>6.0874381780259501E-2</v>
       </c>
@@ -10193,7 +10174,7 @@
       <c r="L7">
         <v>7.1218391851233251</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <f t="shared" si="3"/>
         <v>0.16515959338117869</v>
       </c>
@@ -10203,14 +10184,14 @@
       <c r="O7">
         <v>6.2872529723779467</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <f t="shared" si="4"/>
         <v>0.10071370509579447</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>2.0612945425492066</v>
@@ -10218,7 +10199,7 @@
       <c r="C8">
         <v>2.2928113158625121</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <f t="shared" si="0"/>
         <v>0.11231620155894273</v>
       </c>
@@ -10228,7 +10209,7 @@
       <c r="F8">
         <v>2.3759532383102684</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <f t="shared" si="1"/>
         <v>0.42015084914615164</v>
       </c>
@@ -10238,7 +10219,7 @@
       <c r="I8">
         <v>5.7370683175352637</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <f t="shared" si="2"/>
         <v>0.27556106273640579</v>
       </c>
@@ -10248,7 +10229,7 @@
       <c r="L8">
         <v>6.3735935585442896</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="1">
         <f t="shared" si="3"/>
         <v>0.26712919781683375</v>
       </c>
@@ -10258,7 +10239,7 @@
       <c r="O8">
         <v>4.7943000438381125</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <f t="shared" si="4"/>
         <v>0.20190958409568416</v>
       </c>
@@ -10271,6 +10252,338 @@
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7BC85F1-C09F-4B9B-B11E-3452D0079D61}">
+  <dimension ref="C1:J27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>4.5197021295551201</v>
+      </c>
+      <c r="F2">
+        <v>2.1281780466735798</v>
+      </c>
+      <c r="G2">
+        <v>2.207589209059218</v>
+      </c>
+      <c r="H2">
+        <v>2.663214627042779</v>
+      </c>
+      <c r="I2">
+        <v>2.837321868384854</v>
+      </c>
+      <c r="J2">
+        <v>2.568287972462524</v>
+      </c>
+    </row>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>4.5197021295551183</v>
+      </c>
+      <c r="F3">
+        <v>2.105562013930288</v>
+      </c>
+      <c r="G3">
+        <v>2.2510727036333349</v>
+      </c>
+      <c r="H3">
+        <v>2.769152041163284</v>
+      </c>
+      <c r="I3">
+        <v>2.7449080347887702</v>
+      </c>
+      <c r="J3">
+        <v>2.5303852308873829</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7.8820958553246259</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2.2981770818235088</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.3352707322188273</v>
+      </c>
+      <c r="H4" s="2">
+        <v>6.0375504554926405</v>
+      </c>
+      <c r="I4" s="2">
+        <v>11.361428245732366</v>
+      </c>
+      <c r="J4" s="2">
+        <v>5.9549307792865864</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8.3502835858179676</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2.2640650425011639</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2.5181998556131502</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5.0437205099435367</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5.4623510188892332</v>
+      </c>
+      <c r="J5" s="2">
+        <v>4.7578090316455341</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2">
+        <v>8.4700113001793103</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2.0503344676235664</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2.1745480191730437</v>
+      </c>
+      <c r="H6" s="2">
+        <v>9.5311051900475423</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.1218391851233251</v>
+      </c>
+      <c r="J6" s="2">
+        <v>6.2872529723779467</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2">
+        <v>7.4542098677794399</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2.2928113158625121</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2.3759532383102684</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5.7370683175352637</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.3735935585442896</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4.7943000438381125</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -10285,39 +10598,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
       <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3">
@@ -10340,7 +10653,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B4">
@@ -10363,7 +10676,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5">
@@ -10386,7 +10699,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6">
@@ -10409,7 +10722,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B7">
@@ -10432,66 +10745,66 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="5"/>
+      <c r="B28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28" s="9"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" t="s">
         <v>17</v>
       </c>
-      <c r="C29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="6">
+      <c r="A30" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="4">
         <v>2.128178046673578</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="4">
         <v>2.105562013930288</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="4">
         <v>1.0494413632082391</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="4">
         <v>0.95905123098281442</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="4">
         <v>0.96628285341274633</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="4">
         <v>0.96699566624698974</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J30">
         <f>TTEST(B30:B34,C30:C34,2,2)</f>
@@ -10499,29 +10812,29 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="4">
         <v>2.207589209059218</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="4">
         <v>2.2510727036333349</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="4">
         <v>0.94907410659893265</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="4">
         <v>0.90760134082901345</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="4">
         <v>0.9637196539076307</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="4">
         <v>0.96227632975987243</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J31">
         <f>TTEST(D30:D34,E30:E34,2,2)</f>
@@ -10529,29 +10842,29 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="6">
+      <c r="A32" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="4">
         <v>2.663214627042779</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="4">
         <v>2.769152041163284</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="4">
         <v>1.312878448217691</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="4">
         <v>1.4387964635510739</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="4">
         <v>0.9468744235867097</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="4">
         <v>0.94256390259891798</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J32">
         <f>TTEST(F30:F34,G30:G34,2,2)</f>
@@ -10559,48 +10872,48 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="4">
         <v>2.837321868384854</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="4">
         <v>2.7449080347887702</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="4">
         <v>1.461685608320521</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="4">
         <v>1.399776304499085</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="4">
         <v>0.93970121920264327</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="4">
         <v>0.94356520948612876</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="4">
         <v>2.568287972462524</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="4">
         <v>2.5303852308873829</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="4">
         <v>1.342753732703682</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="4">
         <v>1.273678589060671</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="4">
         <v>0.95059410668617905</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="4">
         <v>0.9520416085172777</v>
       </c>
     </row>
@@ -10612,12 +10925,199 @@
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="F28:G28"/>
   </mergeCells>
+  <conditionalFormatting sqref="B30:C34">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="6" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:E34">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="6" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:G34">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF5050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color theme="6" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A000EF66-E15F-4EA2-9BD3-16DA66EF766E}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>2.13</v>
+      </c>
+      <c r="B1">
+        <v>1.05</v>
+      </c>
+      <c r="C1">
+        <v>0.97</v>
+      </c>
+      <c r="D1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2.21</v>
+      </c>
+      <c r="B2">
+        <v>0.95</v>
+      </c>
+      <c r="C2">
+        <v>0.96</v>
+      </c>
+      <c r="D2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2.77</v>
+      </c>
+      <c r="B3">
+        <v>1.44</v>
+      </c>
+      <c r="C3">
+        <v>0.94</v>
+      </c>
+      <c r="D3">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>7.12</v>
+      </c>
+      <c r="B4">
+        <v>5.01</v>
+      </c>
+      <c r="C4">
+        <v>0.44</v>
+      </c>
+      <c r="D4">
+        <v>9280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>5.95</v>
+      </c>
+      <c r="B5">
+        <v>4.03</v>
+      </c>
+      <c r="C5">
+        <v>0.69</v>
+      </c>
+      <c r="D5">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>4.03</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A5">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B5">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color theme="9" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66FDC195-5525-492E-AF56-3FD76DBD4B19}">
   <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10632,103 +11132,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
+      <c r="A1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="5">
         <v>2.0363856169711649</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>2.5599685466758531</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <f>AVERAGE(B4:C4)</f>
         <v>2.2981770818235088</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>1.136441371328164</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>1.5688883307250781</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <f t="shared" ref="G4:G8" si="0">AVERAGE(E4:F4)</f>
         <v>1.352664851026621</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <v>0.96171795373648428</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>0.94434153407808885</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <f t="shared" ref="J4:J8" si="1">AVERAGE(H4:I4)</f>
         <v>0.95302974390728656</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M4">
         <f>TTEST(B4:B8,B12:B16,2,2)</f>
@@ -10736,41 +11236,41 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>2.245516482845304</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>2.4250249815923501</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <f t="shared" ref="D5:D8" si="2">AVERAGE(B5:C5)</f>
         <v>2.3352707322188273</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>1.170494386653917</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>1.3447638765417991</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <f t="shared" si="0"/>
         <v>1.2576291315978581</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <v>0.95345129573359699</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>0.95005472518839862</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <f t="shared" si="1"/>
         <v>0.95175301046099781</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M5">
         <f>TTEST(C4:C8,C12:C16,2,2)</f>
@@ -10778,41 +11278,41 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="A6" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="5">
         <v>5.8789525166012977</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>6.1961483943839823</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <f t="shared" si="2"/>
         <v>6.0375504554926405</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>4.1603262414367892</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>4.6343397866962706</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <f t="shared" si="0"/>
         <v>4.3973330140665299</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <v>0.67879194169435086</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>0.6838399224868088</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <f t="shared" si="1"/>
         <v>0.68131593209057983</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M6">
         <f>TTEST(D4:D8,D12:D16,2,2)</f>
@@ -10820,41 +11320,41 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>5.748979058393493</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>16.973877433071241</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <f t="shared" si="2"/>
         <v>11.361428245732366</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>4.2589988448253964</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>12.91044353741496</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <f t="shared" si="0"/>
         <v>8.5847211911201775</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="5">
         <v>0.69283765077809933</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <v>-1.37260549785443</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <f t="shared" si="1"/>
         <v>-0.33988392353816532</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M7">
         <f>TTEST(E4:E8,E12:E16,2,2)</f>
@@ -10862,41 +11362,41 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>5.6958207402857104</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>6.2140408182874634</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <f t="shared" si="2"/>
         <v>5.9549307792865864</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>3.7527893214881001</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>4.3014048158927034</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <f t="shared" si="0"/>
         <v>4.0270970686904022</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="5">
         <v>0.69849178298282721</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="5">
         <v>0.68201135501194998</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="5">
         <f t="shared" si="1"/>
         <v>0.6902515689973886</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M8">
         <f>TTEST(F4:F8,F12:F16,2,2)</f>
@@ -10904,20 +11404,20 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="A9" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
       <c r="L9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M9">
         <f>TTEST(G4:G8,G12:G16,2,2)</f>
@@ -10925,24 +11425,24 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
       <c r="L10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M10">
         <f>TTEST(H4:H8,H12:H16,2,2)</f>
@@ -10950,36 +11450,36 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>30</v>
+      <c r="L11" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="M11">
         <f>TTEST(I4:I8,I12:I16,2,2)</f>
@@ -10987,41 +11487,41 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="7">
+      <c r="A12" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="5">
         <v>2.046545336495754</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>2.4815847485065738</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <f>AVERAGE(B12:C12)</f>
         <v>2.2640650425011639</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>1.1055750484380571</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>1.429856712374548</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <f t="shared" ref="G12:G16" si="3">AVERAGE(E12:F12)</f>
         <v>1.2677158804063025</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <v>0.96142586274646968</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>0.90965437351815037</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="5">
         <f t="shared" ref="J12:J16" si="4">AVERAGE(H12:I12)</f>
         <v>0.93554011813230997</v>
       </c>
       <c r="L12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M12">
         <f>TTEST(J4:J8,J12:J16,2,2)</f>
@@ -11029,71 +11529,71 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>2.2395185954139079</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>2.796881115812393</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <f t="shared" ref="D13:D16" si="5">AVERAGE(B13:C13)</f>
         <v>2.5181998556131502</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>1.0754492410530361</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>1.534063285366595</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="5">
         <f t="shared" si="3"/>
         <v>1.3047562632098155</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="5">
         <v>0.95380841896497426</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="5">
         <v>0.88523831284930565</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="5">
         <f t="shared" si="4"/>
         <v>0.91952336590714001</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="7">
+      <c r="A14" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="5">
         <v>5.2576866473044346</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>4.8297543725826388</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <f t="shared" si="5"/>
         <v>5.0437205099435367</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>3.4608132305724579</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>3.027706073744874</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <f t="shared" si="3"/>
         <v>3.2442596521586662</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <v>0.74332013534249319</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>0.64912003640280358</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="5">
         <f t="shared" si="4"/>
         <v>0.69622008587264839</v>
       </c>
@@ -11103,36 +11603,36 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>5.2138785711668252</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>5.7108234666116422</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <f t="shared" si="5"/>
         <v>5.4623510188892332</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>2.949152478290987</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <v>3.3975105587643069</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <f t="shared" si="3"/>
         <v>3.1733315185276467</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="5">
         <v>0.74757972914725623</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>0.50942439123721994</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="5">
         <f t="shared" si="4"/>
         <v>0.62850206019223809</v>
       </c>
@@ -11142,36 +11642,36 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>4.8481865655520311</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>4.6674314977390372</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <f t="shared" si="5"/>
         <v>4.7578090316455341</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>2.8576432976255912</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>3.242423585171653</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <f t="shared" si="3"/>
         <v>3.0500334413986221</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <v>0.7817465833373648</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>0.67230909638915659</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="5">
         <f t="shared" si="4"/>
         <v>0.72702783986326069</v>
       </c>
@@ -11200,17 +11700,37 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:J10"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="H10:J10"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B8">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:G8">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:G16">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11220,7 +11740,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C8">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11230,7 +11750,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11240,27 +11760,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:J8">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12:G16">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:G8">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11270,7 +11770,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:J8">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11278,9 +11778,17 @@
         <color rgb="FFFCFCFF"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF5050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:J16">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11288,134 +11796,182 @@
         <color rgb="FFFCFCFF"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF5050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:D8">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:G8">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:D16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12:G16">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49073274-9D30-44D4-A58F-53158582F014}">
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="A1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
+      <c r="A3" s="3"/>
       <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
         <v>33</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
       <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
         <v>33</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
       <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
         <v>33</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>34</v>
       </c>
-      <c r="L3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
         <v>1.78635893725304</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>1.8759071739972839</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>2.4887372916203758</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>2.0503344676235664</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>1.0049648421862361</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>1.214879559358605</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>1.484803568039637</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>1.2348826565281594</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>0.95519947552036888</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="4">
         <v>0.96687772806594163</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <v>0.94972207827015187</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="4">
         <v>0.9572664272854875</v>
       </c>
       <c r="O4">
@@ -11432,43 +11988,43 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>2.086909898456597</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>2.0334241021933619</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>2.4033100568691732</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>2.1745480191730437</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>1.115633991038075</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>1.2376940476052971</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <v>1.372843654748569</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="4">
         <v>1.242057231130647</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <v>0.93885611327386687</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="4">
         <v>0.96108174460171281</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <v>0.95311447165133656</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="4">
         <v>0.95101744317563863</v>
       </c>
       <c r="O5">
@@ -11485,43 +12041,43 @@
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4">
         <v>6.9427797674268206</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>10.43738983742605</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>11.21314596528976</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>9.5311051900475423</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>4.6273726290641948</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="4">
         <v>9.5036559824011793</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>10.351646960947861</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>8.1608918574710767</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>0.2718759426539834</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="4">
         <v>-6.4417119478008766E-2</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
         <v>-8.8338071834548337E-3</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="4">
         <v>6.6208338664173264E-2</v>
       </c>
       <c r="O6">
@@ -11538,202 +12094,202 @@
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>6.2043426026508488</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>9.0623327955438082</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>6.098842157175322</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>7.1218391851233251</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>3.8907359780392752</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="4">
         <v>6.5956337495617481</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>4.5521694332077658</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>5.0128463869362632</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <v>0.41852620813137142</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="4">
         <v>0.19756834108787899</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
         <v>0.70155832852541589</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="4">
         <v>0.43921762591488878</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>6.1635285332548424</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>7.8169191371184414</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>4.8813112467605562</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>6.2872529723779467</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>4.2884891993664684</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>5.7078034208821142</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>3.1238031972539342</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>4.3733652725008385</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>0.42615127141171938</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="4">
         <v>0.40296570290974421</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <v>0.80882210417522982</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="4">
         <v>0.54597969283223113</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
+      <c r="A11" s="3"/>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
       <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
         <v>33</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" t="s">
-        <v>36</v>
-      </c>
       <c r="J11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
         <v>33</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>34</v>
       </c>
-      <c r="L11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="6">
+      <c r="A12" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="4">
         <v>2.4855914798135901</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>2.355913227953716</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>2.0369292398202292</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>2.2928113158625121</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="4">
         <v>1.4180845242911551</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="4">
         <v>1.501635227832566</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>1.1027042107864311</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="4">
         <v>1.3408079876367174</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
         <v>0.80741695136704839</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="4">
         <v>0.94073046027380214</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="4">
         <v>0.96178750749125852</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="4">
         <v>0.90331163971070294</v>
       </c>
       <c r="O12">
@@ -11750,43 +12306,43 @@
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>2.4780206279088439</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>2.4055290698938201</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>2.2443100171281412</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>2.3759532383102684</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <v>1.4594443930263761</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="4">
         <v>1.4572678590935531</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>1.0723093992186581</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="4">
         <v>1.3296738837795292</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="4">
         <v>0.80858834036443561</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="4">
         <v>0.93820772392750307</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="4">
         <v>0.95361055492036395</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="4">
         <v>0.90013553973743432</v>
       </c>
       <c r="O13">
@@ -11803,43 +12359,43 @@
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="6">
+      <c r="A14" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="4">
         <v>6.1186485921999969</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>5.6857997265737739</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>5.4067566338320212</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <v>5.7370683175352637</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <v>4.2180903189697263</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="4">
         <v>3.918979639333275</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="4">
         <v>3.557860716889099</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>3.8983102250640336</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="4">
         <v>-0.1041717351781395</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="4">
         <v>0.65179680575285759</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="4">
         <v>0.7285586246805732</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="4">
         <v>0.42539456508509715</v>
       </c>
       <c r="O14">
@@ -11856,89 +12412,140 @@
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>7.9999676164344562</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
         <v>6.0767821984060788</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>5.0440308607923328</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>6.3735935585442896</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <v>5.4857680000000002</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="4">
         <v>3.9211614712772458</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="4">
         <v>2.892683633761747</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="4">
         <v>4.0998710350129981</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
         <v>-0.88756563055399496</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="4">
         <v>0.60226210046594453</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="4">
         <v>0.76375758496858559</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="4">
         <v>0.1594846849601784</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="4">
         <v>4.1972665327909606</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="4">
         <v>5.6045169518598046</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="4">
         <v>4.5811166468635731</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="4">
         <v>4.7943000438381125</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="4">
         <v>2.7102933473129269</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="4">
         <v>4.0672740507781828</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="4">
         <v>2.6169642965314641</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="4">
         <v>3.131510564874191</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="4">
         <v>0.48041249353112347</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="4">
         <v>0.6616812960229197</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="4">
         <v>0.80512994673629734</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="4">
         <v>0.64907457876344676</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <f>TTEST(B4:B8,B12:B16,2,2)</f>
+        <v>0.99042947266231773</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ref="C18:M18" si="0">TTEST(C4:C8,C12:C16,2,2)</f>
+        <v>0.38635563472377732</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>0.40397252159519037</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>0.52553354280274056</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>0.9498510673952536</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>0.3064757207730866</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>0.29577268253550204</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>0.41006465702662998</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>0.31265765111796434</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>0.25922438894496957</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="0"/>
+        <v>0.40808731750304783</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="0"/>
+        <v>0.94555256540804966</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="A9:M9"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="F10:I10"/>
@@ -11946,13 +12553,72 @@
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A1:M1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B4:E8">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:I8">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4:M8">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF5050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:E16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:I16">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12:M16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF5050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8DB40-FE70-4D47-8AF4-0AC46DFB4898}">
   <dimension ref="A2:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11964,15 +12630,15 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="8">
+        <v>52</v>
+      </c>
+      <c r="B2" s="6">
         <v>0.15210648148148148</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>0.1522337962962963</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <f>C2-B2</f>
         <v>1.2731481481481621E-4</v>
       </c>
@@ -11984,13 +12650,13 @@
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="8">
         <v>45730.152233796296</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="8">
         <v>45730.159791666665</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <f>C3-B3</f>
         <v>7.5578703690553084E-3</v>
       </c>
@@ -12001,15 +12667,15 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="10">
+        <v>51</v>
+      </c>
+      <c r="B4" s="8">
         <v>45730.159791666665</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="8">
         <v>45730.194768518515</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <f>C4-B4</f>
         <v>3.4976851849933155E-2</v>
       </c>
@@ -12020,12 +12686,12 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="10">
+        <v>53</v>
+      </c>
+      <c r="B5" s="8">
         <v>45730.194768518515</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>45730.211284722223</v>
       </c>
       <c r="D5">
@@ -12042,12 +12708,12 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="9">
+        <v>54</v>
+      </c>
+      <c r="B6" s="7">
         <v>45728.435162037036</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>45728.669618055559</v>
       </c>
       <c r="D6">
@@ -12055,10 +12721,10 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="10">
+      <c r="B7" s="8">
         <v>45729.779351851852</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="8">
         <v>45729.784444444442</v>
       </c>
       <c r="D7">
@@ -12066,10 +12732,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="10">
+      <c r="B8" s="8">
         <v>45729.858622685184</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="8">
         <v>45729.863229166665</v>
       </c>
       <c r="D8">
@@ -12077,10 +12743,10 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="10">
+      <c r="B9" s="8">
         <v>45729.936863425923</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="8">
         <v>45729.942060185182</v>
       </c>
       <c r="D9">
@@ -12088,20 +12754,19 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="10">
+      <c r="B11" s="8">
         <v>45730.211284722223</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="8">
         <v>45730.223773148151</v>
       </c>
-      <c r="D11" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14CFF2F0-FA38-453E-8C4B-784DB7CE81B3}">
   <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12119,82 +12784,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>12</v>
+      <c r="C2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="A3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="5">
         <v>2.128178046673578</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>2.2640650425011639</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>2.2928113158625121</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>1.0494413632082391</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>1.2677158804063025</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>1.3408079876367174</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <v>0.96628285341274633</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <v>0.93554011813230997</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="5">
         <v>0.90331163971070294</v>
       </c>
       <c r="L3">
@@ -12211,34 +12876,34 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>2.207589209059218</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>2.5181998556131502</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>2.3759532383102684</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>0.94907410659893265</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>1.3047562632098155</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>1.3296738837795292</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <v>0.9637196539076307</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>0.91952336590714001</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <v>0.90013553973743432</v>
       </c>
       <c r="L4">
@@ -12255,34 +12920,34 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7">
+      <c r="A5" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="5">
         <v>2.663214627042779</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>5.0437205099435367</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>5.7370683175352637</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>1.312878448217691</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>3.2442596521586662</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>3.8983102250640336</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <v>0.9468744235867097</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>0.69622008587264839</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <v>0.42539456508509715</v>
       </c>
       <c r="L5">
@@ -12299,89 +12964,89 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>2.837321868384854</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>5.4623510188892332</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>6.3735935585442896</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>1.461685608320521</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>3.1733315185276467</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>4.0998710350129981</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <v>0.93970121920264327</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>0.62850206019223809</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <v>0.1594846849601784</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>2.568287972462524</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>4.7578090316455341</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>4.7943000438381125</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>1.342753732703682</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>3.0500334413986221</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <v>3.131510564874191</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="5">
         <v>0.95059410668617905</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <v>0.72702783986326069</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <v>0.64907457876344676</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+      <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+      <c r="A15" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12389,11 +13054,65 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B3:D7">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:G7">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:J7">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF5050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color theme="9" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7714DB-FAC8-4704-8981-315012BF51AC}">
   <dimension ref="A2:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12402,522 +13121,191 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
+      <c r="A2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="5">
         <v>2.128178046673578</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>1.0494413632082391</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>0.96628285341274633</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>2.207589209059218</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>0.94907410659893265</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>0.9637196539076307</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="A6" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="5">
         <v>2.663214627042779</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>1.312878448217691</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>0.9468744235867097</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>2.837321868384854</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>1.461685608320521</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>0.93970121920264327</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>2.568287972462524</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>1.342753732703682</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>0.95059410668617905</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
+      <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+      <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+      <c r="A15" s="2"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
+      <c r="A16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98074A34-AA82-4CB2-B9A0-78FC7943A6C8}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="103.21875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="44.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="103.21875" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="3" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B6" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7BC85F1-C09F-4B9B-B11E-3452D0079D61}">
-  <dimension ref="C1:J27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="E1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3">
-        <v>4.5197021295551201</v>
-      </c>
-      <c r="F2">
-        <v>2.128178046673578</v>
-      </c>
-      <c r="G2">
-        <v>2.207589209059218</v>
-      </c>
-      <c r="H2">
-        <v>2.663214627042779</v>
-      </c>
-      <c r="I2">
-        <v>2.837321868384854</v>
-      </c>
-      <c r="J2">
-        <v>2.568287972462524</v>
-      </c>
-    </row>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>4.5197021295551183</v>
-      </c>
-      <c r="F3">
-        <v>2.105562013930288</v>
-      </c>
-      <c r="G3">
-        <v>2.2510727036333349</v>
-      </c>
-      <c r="H3">
-        <v>2.769152041163284</v>
-      </c>
-      <c r="I3">
-        <v>2.7449080347887702</v>
-      </c>
-      <c r="J3">
-        <v>2.5303852308873829</v>
-      </c>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="3">
-        <v>7.8820958553246259</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2.2981770818235088</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2.3352707322188273</v>
-      </c>
-      <c r="H4" s="3">
-        <v>6.0375504554926405</v>
-      </c>
-      <c r="I4" s="3">
-        <v>11.361428245732366</v>
-      </c>
-      <c r="J4" s="3">
-        <v>5.9549307792865864</v>
-      </c>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="3">
-        <v>8.3502835858179676</v>
-      </c>
-      <c r="F5" s="3">
-        <v>2.2640650425011639</v>
-      </c>
-      <c r="G5" s="3">
-        <v>2.5181998556131502</v>
-      </c>
-      <c r="H5" s="3">
-        <v>5.0437205099435367</v>
-      </c>
-      <c r="I5" s="3">
-        <v>5.4623510188892332</v>
-      </c>
-      <c r="J5" s="3">
-        <v>4.7578090316455341</v>
-      </c>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3">
-        <v>8.4700113001793103</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2.0503344676235664</v>
-      </c>
-      <c r="G6" s="3">
-        <v>2.1745480191730437</v>
-      </c>
-      <c r="H6" s="3">
-        <v>9.5311051900475423</v>
-      </c>
-      <c r="I6" s="3">
-        <v>7.1218391851233251</v>
-      </c>
-      <c r="J6" s="3">
-        <v>6.2872529723779467</v>
-      </c>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="3">
-        <v>7.4542098677794399</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2.2928113158625121</v>
-      </c>
-      <c r="G7" s="3">
-        <v>2.3759532383102684</v>
-      </c>
-      <c r="H7" s="3">
-        <v>5.7370683175352637</v>
-      </c>
-      <c r="I7" s="3">
-        <v>6.3735935585442896</v>
-      </c>
-      <c r="J7" s="3">
-        <v>4.7943000438381125</v>
-      </c>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/Evaluación de métricas.xlsx
+++ b/Evaluación de métricas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="185" documentId="13_ncr:1_{FA4D00DD-8E8B-4DA4-8141-A139AE06F642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{157C48A6-D3AE-4E37-BC67-2EE22FB50008}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{D195F59A-6A96-4642-803F-E5122D0BFA4A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{D195F59A-6A96-4642-803F-E5122D0BFA4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -342,41 +342,41 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9517,6 +9517,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -9841,31 +9845,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="14" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="16" t="s">
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
       <c r="K1" s="18" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
@@ -10269,19 +10273,19 @@
       <c r="E1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="14" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10598,16 +10602,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
@@ -10744,19 +10748,19 @@
         <v>0.9520416085172777</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B28" s="9" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9" t="s">
+      <c r="C28" s="20"/>
+      <c r="D28" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9" t="s">
+      <c r="E28" s="20"/>
+      <c r="F28" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="G28" s="9"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
@@ -10782,7 +10786,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B30" s="4">
@@ -10812,7 +10816,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B31" s="4">
@@ -10842,7 +10846,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B32" s="4">
@@ -10872,7 +10876,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B33" s="4">
@@ -10895,7 +10899,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B34" s="4">
@@ -10926,12 +10930,12 @@
     <mergeCell ref="F28:G28"/>
   </mergeCells>
   <conditionalFormatting sqref="B30:C34">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
+        <color theme="6" tint="0.39997558519241921"/>
         <color theme="0"/>
-        <color rgb="FFFF5050"/>
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -10942,7 +10946,17 @@
         <color theme="0"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:E34">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10950,8 +10964,6 @@
         <color theme="0"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D30:E34">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -10960,30 +10972,22 @@
         <color rgb="FFFF5050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:G34">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
+        <color theme="0"/>
         <color theme="6" tint="0.39997558519241921"/>
-        <color theme="0"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F30:G34">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
         <color rgb="FFFF5050"/>
         <color theme="0"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="0"/>
-        <color theme="6" tint="0.39997558519241921"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -11132,36 +11136,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9" t="s">
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
@@ -11194,7 +11198,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="5">
@@ -11236,7 +11240,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="5">
@@ -11278,7 +11282,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B6" s="5">
@@ -11320,7 +11324,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5">
@@ -11362,7 +11366,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="5">
@@ -11404,18 +11408,18 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
       <c r="L9" t="s">
         <v>26</v>
       </c>
@@ -11426,21 +11430,21 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
       <c r="L10" t="s">
         <v>27</v>
       </c>
@@ -11487,7 +11491,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="5">
@@ -11529,7 +11533,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B13" s="5">
@@ -11564,7 +11568,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B14" s="5">
@@ -11603,7 +11607,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="5">
@@ -11642,7 +11646,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="5">
@@ -11700,14 +11704,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A9:J9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B8">
     <cfRule type="colorScale" priority="14">
@@ -11716,6 +11720,26 @@
         <cfvo type="max"/>
         <color rgb="FFFCFCFF"/>
         <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:D8">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:D16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -11759,74 +11783,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:J8">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:J8">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF5050"/>
-        <color theme="0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:J16">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF5050"/>
-        <color theme="0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:D8">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="0"/>
-        <color rgb="FFFF5050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E4:G8">
     <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="0"/>
-        <color rgb="FFFF5050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12:D16">
-    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11845,6 +11803,52 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E4:J8">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:J8">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF5050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:J16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF5050"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11858,42 +11862,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9" t="s">
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
@@ -11935,7 +11939,7 @@
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="4">
@@ -11988,7 +11992,7 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4">
@@ -12041,7 +12045,7 @@
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B6" s="4">
@@ -12094,7 +12098,7 @@
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="4">
@@ -12135,7 +12139,7 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="4">
@@ -12176,42 +12180,42 @@
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9" t="s">
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
@@ -12253,7 +12257,7 @@
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="4">
@@ -12306,7 +12310,7 @@
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B13" s="4">
@@ -12359,7 +12363,7 @@
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B14" s="4">
@@ -12412,7 +12416,7 @@
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="4">
@@ -12453,7 +12457,7 @@
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="4">
@@ -12564,8 +12568,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B12:E16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F4:I8">
     <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF5050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:I16">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -12581,26 +12605,6 @@
         <cfvo type="max"/>
         <color rgb="FFFF5050"/>
         <color theme="0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12:E16">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="0"/>
-        <color rgb="FFFF5050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12:I16">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="0"/>
-        <color rgb="FFFF5050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -12785,21 +12789,21 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9" t="s">
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -12832,7 +12836,7 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="5">
@@ -12876,7 +12880,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="5">
@@ -12920,7 +12924,7 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="5">
@@ -12964,7 +12968,7 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="5">
@@ -12996,7 +13000,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="5">
@@ -13055,6 +13059,14 @@
     <mergeCell ref="H1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:D7">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -13063,7 +13075,9 @@
         <color rgb="FFFF5050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:G7">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -13071,8 +13085,6 @@
         <color theme="0"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G7">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -13081,30 +13093,22 @@
         <color rgb="FFFF5050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:J7">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
+        <color theme="0"/>
         <color theme="9" tint="0.39997558519241921"/>
-        <color theme="0"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:J7">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
         <color rgb="FFFF5050"/>
         <color theme="0"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="0"/>
-        <color theme="9" tint="0.39997558519241921"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -13131,12 +13135,12 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="5">
@@ -13150,7 +13154,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="5">
@@ -13164,7 +13168,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B6" s="5">
@@ -13178,7 +13182,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5">
@@ -13192,7 +13196,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="5">
@@ -13281,7 +13285,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
@@ -13297,7 +13301,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
